--- a/praktikumsplaner-backend/src/test/resources/de/muenchen/oss/praktikumsplaner/service/ExcelNwkInvalidData.xlsx
+++ b/praktikumsplaner-backend/src/test/resources/de/muenchen/oss/praktikumsplaner/service/ExcelNwkInvalidData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daniel.nischwitz\Documents\Praktikumsplaner\praktikumsplaner-backend\src\test\resources\de\muenchen\oss\praktikumsplaner\service\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rene.zarwel\develop\Projekte\Praktikumsplaner\praktikumsplaner-backend\src\test\resources\de\muenchen\oss\praktikumsplaner\service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C0117C-8E87-425C-833F-5CA40C0CA3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F74E16B-5A29-47D6-89EB-D8846F997D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{E95CBEE5-BDCF-48D0-B574-A8FA4EA1B085}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E95CBEE5-BDCF-48D0-B574-A8FA4EA1B085}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -105,6 +105,21 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>LLB</t>
+  </si>
+  <si>
+    <t>QE2</t>
+  </si>
+  <si>
+    <t>KFB</t>
+  </si>
+  <si>
+    <t>VFAK</t>
+  </si>
+  <si>
+    <t>PUMA</t>
   </si>
 </sst>
 </file>
@@ -210,9 +225,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -250,7 +265,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -356,7 +371,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -498,7 +513,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -507,16 +522,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40CCF9E-2FB7-4310-91B7-7540413BFD8B}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.69921875" customWidth="1"/>
-    <col min="2" max="2" width="16.69921875" customWidth="1"/>
-    <col min="3" max="3" width="15.69921875" customWidth="1"/>
-    <col min="4" max="4" width="18.09765625" customWidth="1"/>
-    <col min="5" max="5" width="20.8984375" customWidth="1"/>
+    <col min="1" max="1" width="15.75" customWidth="1"/>
+    <col min="2" max="2" width="16.75" customWidth="1"/>
+    <col min="3" max="3" width="15.75" customWidth="1"/>
+    <col min="4" max="4" width="18.125" customWidth="1"/>
+    <col min="5" max="5" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="27.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -533,7 +548,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -550,7 +565,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -563,7 +578,7 @@
       </c>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -576,13 +591,13 @@
       </c>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>16</v>
@@ -591,7 +606,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -606,7 +621,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
@@ -614,14 +629,14 @@
         <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -629,14 +644,14 @@
         <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -647,7 +662,7 @@
       </c>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
@@ -664,7 +679,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
@@ -672,7 +687,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>21</v>
@@ -681,7 +696,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>7</v>
       </c>
@@ -690,7 +705,7 @@
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>8</v>
@@ -699,16 +714,16 @@
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -717,7 +732,7 @@
       </c>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -726,7 +741,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>7</v>
       </c>
@@ -745,14 +760,17 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C12 C21:C1048576" xr:uid="{632E850D-EAD0-4075-AEC5-93E397686794}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C21:C1048576" xr:uid="{632E850D-EAD0-4075-AEC5-93E397686794}">
       <formula1>"BWI,BSC,VI,FISI"</formula1>
     </dataValidation>
     <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D12" xr:uid="{E3003509-3CA1-4A0E-A56E-2E5DE0CE4E34}">
       <formula1>2010</formula1>
       <formula2>2500</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C17" xr:uid="{7200B176-D41B-4900-A776-0B9C133BD3B5}">
+      <formula1>"BWI,BSC,VI,FISI,LLB,PUMA,QE3,QE2,KFB,VFAK"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
